--- a/BUK/Permisos/BUK_permisos.xlsx
+++ b/BUK/Permisos/BUK_permisos.xlsx
@@ -61,7 +61,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Fecha Generación: 26/05/2026 a las 05:32PM</t>
+          <t>Fecha Generación: 28/05/2026 a las 02:34PM</t>
         </is>
       </c>
     </row>
